--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87024</v>
+        <v>87027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87027</v>
+        <v>87029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87029</v>
+        <v>87033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87033</v>
+        <v>87034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87034</v>
+        <v>87062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87062</v>
+        <v>87068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87068</v>
+        <v>87069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87069</v>
+        <v>87074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87074</v>
+        <v>87078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87078</v>
+        <v>87080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129419078</v>
       </c>
       <c r="B2" t="n">
-        <v>87080</v>
+        <v>87375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130958995</v>
+        <v>130958994</v>
       </c>
       <c r="B3" t="n">
-        <v>87281</v>
+        <v>87375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>653457</v>
+        <v>653475</v>
       </c>
       <c r="R3" t="n">
-        <v>6556385</v>
+        <v>6556413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130958994</v>
+        <v>130958995</v>
       </c>
       <c r="B4" t="n">
-        <v>87281</v>
+        <v>87375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>653475</v>
+        <v>653457</v>
       </c>
       <c r="R4" t="n">
-        <v>6556413</v>
+        <v>6556385</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 26902-2024 artfynd.xlsx
+++ b/artfynd/A 26902-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419078</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t>Sand- och åsbarrskogar i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130958994</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,8 +994,18 @@
           <t>Sand- och åsbarrskogar i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130958995</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>